--- a/data/trans_orig/IP16A04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A04-Habitat-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>38329</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37435</t>
+          <t>37815</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78478</t>
+          <t>78666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31799</t>
+          <t>31581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56865</t>
+          <t>56285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21841</t>
+          <t>21522</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35217</t>
+          <t>35123</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59639</t>
+          <t>59440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120311</t>
+          <t>120599</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138733</t>
+          <t>136965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143246</t>
+          <t>143247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>261182</t>
+          <t>261004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267853</t>
+          <t>267851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47968</t>
+          <t>47777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99594</t>
+          <t>99388</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40089</t>
+          <t>40319</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>48189</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90331</t>
+          <t>90449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46478</t>
+          <t>46021</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97477</t>
+          <t>97448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183815</t>
+          <t>183862</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>185901</t>
+          <t>185947</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190873</t>
+          <t>190876</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>372227</t>
+          <t>372764</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377842</t>
+          <t>377841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>593</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>26728</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31482</t>
+          <t>31471</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25133</t>
+          <t>25605</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54747</t>
+          <t>54683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60146</t>
+          <t>60138</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>531</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48965</t>
+          <t>48839</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45678</t>
+          <t>46150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97866</t>
+          <t>97330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102646</t>
+          <t>102648</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38710</t>
+          <t>39319</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76576</t>
+          <t>76563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154026</t>
+          <t>154486</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160700</t>
+          <t>161039</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>143185</t>
+          <t>143430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300591</t>
+          <t>300104</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308085</t>
+          <t>308086</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP16A04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A04-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1070,102 +1070,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3503</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3318</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3326</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,61%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4149</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4286</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40608</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37803</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>40978</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>38329</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>38321</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,39%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>92,01%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>40608</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>37815</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,55%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>127</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78666</t>
+          <t>78803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3865</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3542</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3409</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4001</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34450</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31258</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>34450</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>31581</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>89,92%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>95</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56285</t>
+          <t>56877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4081</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>767</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4155</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4186</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3694</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5501</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1580</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5054</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38004</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34736</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,49%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>24910</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21522</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>21491</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>83,7%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38004</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>90,48%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>88</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59440</t>
+          <t>58993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6599</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4706</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5206</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6954</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>141735</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>137320</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143249</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,41%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>123869</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>120599</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>120099</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,85%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>141735</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136965</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143247</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>95,17%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>400</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>261004</t>
+          <t>261975</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267851</t>
+          <t>267858</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2787,42 +2787,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>41042</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2900,52 +2900,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>41042</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>41042</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>41042</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>625</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2716</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3312</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50338</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47838</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,87%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>51737</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>50338</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>47777</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,75%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>149</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99388</t>
+          <t>99984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51737</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51737</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51737</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3360,102 +3360,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3171</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3719</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>8,56%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3039</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4257</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4208</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>50621</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>48057</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,81%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>42802</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40319</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>39710</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,56%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>91,44%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>50621</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>48189</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,07%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>145</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90449</t>
+          <t>90400</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3940</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>641</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3920</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3679</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3277</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49300</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>46001</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>49300</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>46021</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>92,15%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>134</t>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97448</t>
+          <t>97046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3177</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5531</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4159,69 +4159,69 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>189605</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>185784</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>190870</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>186365</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>183862</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>183815</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>189605</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>185947</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>190876</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>536</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>372764</t>
+          <t>372223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377841</t>
+          <t>377846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3779</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1950</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5336</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,08%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3114</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28067</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24940</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30114</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26728</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>31471</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>26734</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31465</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,92%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,36%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28067</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25605</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54683</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60138</t>
+          <t>60133</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4579</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4491</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3611</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>534</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49044</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45741</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>52112</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48839</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>48927</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,55%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>91,59%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>49044</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>46150</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,74%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>157</t>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97330</t>
+          <t>98120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102648</t>
+          <t>102645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>33948</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>772</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3787</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3933</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>9,12%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3859</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3813</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>42334</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>39319</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>39173</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>43106</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>90,88%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>110</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76563</t>
+          <t>76517</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>43106</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>43106</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>43106</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4795</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4028</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1497</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8050</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8802</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4695</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>146755</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>143330</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>158508</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>154486</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>161039</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>153734</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>161075</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,52%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>146755</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>143430</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300104</t>
+          <t>300927</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308086</t>
+          <t>308222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
